--- a/sample-data/demo-input.xlsx
+++ b/sample-data/demo-input.xlsx
@@ -7,7 +7,8 @@
     <sheet name="Codes" sheetId="2" r:id="rId2"/>
     <sheet name="Shifts" sheetId="3" r:id="rId3"/>
     <sheet name="Breaks" sheetId="4" r:id="rId4"/>
-    <sheet name="Settings" sheetId="5" r:id="rId5"/>
+    <sheet name="Order" sheetId="5" r:id="rId5"/>
+    <sheet name="Settings" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -656,7 +657,7 @@
         <v>Family</v>
       </c>
       <c r="C1" t="str">
-        <v>Unit time (min)</v>
+        <v>Unit time (s)</v>
       </c>
       <c r="D1" t="str">
         <v>Description</v>
@@ -670,7 +671,7 @@
         <v>Sealant</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>360</v>
       </c>
       <c r="D2" t="str">
         <v>Sealant 100 ml</v>
@@ -684,7 +685,7 @@
         <v>Sealant</v>
       </c>
       <c r="C3">
-        <v>7.5</v>
+        <v>450</v>
       </c>
       <c r="D3" t="str">
         <v>Sealant 220 ml</v>
@@ -698,7 +699,7 @@
         <v>Sealant</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>540</v>
       </c>
       <c r="D4" t="str">
         <v>Sealant 310 ml</v>
@@ -712,7 +713,7 @@
         <v>Adhesive</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="D5" t="str">
         <v>Adhesive standard</v>
@@ -726,7 +727,7 @@
         <v>Adhesive</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>390</v>
       </c>
       <c r="D6" t="str">
         <v>Adhesive premium</v>
@@ -740,7 +741,7 @@
         <v>Adhesive</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>480</v>
       </c>
       <c r="D7" t="str">
         <v>Adhesive flex</v>
@@ -754,7 +755,7 @@
         <v>Primer</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>240</v>
       </c>
       <c r="D8" t="str">
         <v>Primer fast-dry</v>
@@ -768,7 +769,7 @@
         <v>Primer</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>330</v>
       </c>
       <c r="D9" t="str">
         <v>Primer all-weather</v>
@@ -782,7 +783,7 @@
         <v>Primer</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>420</v>
       </c>
       <c r="D10" t="str">
         <v>Primer marine</v>
@@ -796,7 +797,7 @@
         <v>Coating</v>
       </c>
       <c r="C11">
-        <v>8.5</v>
+        <v>510</v>
       </c>
       <c r="D11" t="str">
         <v>Coating gloss</v>
@@ -810,7 +811,7 @@
         <v>Coating</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="D12" t="str">
         <v>Coating satin</v>
@@ -824,7 +825,7 @@
         <v>Coating</v>
       </c>
       <c r="C13">
-        <v>12.5</v>
+        <v>750</v>
       </c>
       <c r="D13" t="str">
         <v>Coating industrial</v>
@@ -838,7 +839,7 @@
         <v>Cleaner</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="D14" t="str">
         <v>Cleaner daily</v>
@@ -852,7 +853,7 @@
         <v>Cleaner</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>270</v>
       </c>
       <c r="D15" t="str">
         <v>Cleaner heavy-duty</v>
@@ -866,7 +867,7 @@
         <v>Lubricant</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="D16" t="str">
         <v>Lubricant light</v>
@@ -880,7 +881,7 @@
         <v>Lubricant</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>360</v>
       </c>
       <c r="D17" t="str">
         <v>Lubricant heavy</v>
@@ -894,7 +895,7 @@
         <v>Resin</v>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>660</v>
       </c>
       <c r="D18" t="str">
         <v>Resin epoxy</v>
@@ -908,7 +909,7 @@
         <v>Resin</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>780</v>
       </c>
       <c r="D19" t="str">
         <v>Resin casting</v>
@@ -1011,6 +1012,226 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Qty</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Produced</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>RS-190</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>RS-300</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CO-130</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CO-170</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CO-290</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CL-140</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CL-280</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SL-100</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SL-220</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SL-310</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LB-160</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LB-270</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AD-110</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AD-150</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AD-240</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>PR-120</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>PR-180</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PR-260</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
